--- a/assessment_forms/029_stroke_rehabilitation_assessment_quiz--assessment_forms.xlsx
+++ b/assessment_forms/029_stroke_rehabilitation_assessment_quiz--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cerebral_cortex</t>
+          <t>cerebral cortex</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1_week</t>
+          <t>1 week</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2_weeks</t>
+          <t>2 weeks</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3_weeks</t>
+          <t>3 weeks</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4_weeks</t>
+          <t>4 weeks</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6_weeks</t>
+          <t>6 weeks</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>15_minutes</t>
+          <t>15 minutes</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>30_minutes</t>
+          <t>30 minutes</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>60_minutes</t>
+          <t>60 minutes</t>
         </is>
       </c>
     </row>
